--- a/docs/verification/files/rocscience/vp049.xlsx
+++ b/docs/verification/files/rocscience/vp049.xlsx
@@ -1923,13 +1923,13 @@
           <t>Anchor</t>
         </is>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="3" t="str">
         <f>IF($G3="","",IFERROR(VLOOKUP($G3,$Z$8:$AB$11,2,0),""))</f>
-        <v/>
-      </c>
-      <c r="I3" s="3">
+        <v>Axial</v>
+      </c>
+      <c r="I3" s="3" t="str">
         <f>IF($G3="","",IFERROR(VLOOKUP($G3,$Z$8:$AB$11,3,0),""))</f>
-        <v/>
+        <v>Active</v>
       </c>
       <c r="J3" s="3">
         <v>15043.1125</v>
@@ -1994,13 +1994,13 @@
           <t>Anchor</t>
         </is>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="3" t="str">
         <f>IF($G4="","",IFERROR(VLOOKUP($G4,$Z$8:$AB$11,2,0),""))</f>
-        <v/>
-      </c>
-      <c r="I4" s="3">
+        <v>Axial</v>
+      </c>
+      <c r="I4" s="3" t="str">
         <f>IF($G4="","",IFERROR(VLOOKUP($G4,$Z$8:$AB$11,3,0),""))</f>
-        <v/>
+        <v>Active</v>
       </c>
       <c r="J4" s="3">
         <v>20527.1625</v>

--- a/docs/verification/files/rocscience/vp049.xlsx
+++ b/docs/verification/files/rocscience/vp049.xlsx
@@ -5429,7 +5429,23 @@
       </c>
       <c r="D10" s="48" t="inlineStr">
         <is>
-          <t>gsat</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>g</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+            </rPr>
+            <t>sat</t>
+          </r>
         </is>
       </c>
       <c r="E10" s="44" t="inlineStr">

--- a/docs/verification/files/rocscience/vp049.xlsx
+++ b/docs/verification/files/rocscience/vp049.xlsx
@@ -2697,7 +2697,26 @@
       </c>
       <c r="H2" s="40" t="inlineStr">
         <is>
-          <t>qp</t>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>q</t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>p</t>
+          </r>
         </is>
       </c>
       <c r="I2" s="40" t="inlineStr">
@@ -5560,12 +5579,64 @@
       </c>
       <c r="AA10" s="46" t="inlineStr">
         <is>
-          <t>s(g)</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>s</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>g</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>)</t>
+          </r>
         </is>
       </c>
       <c r="AB10" s="46" t="inlineStr">
         <is>
-          <t>s(c)</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>s</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>(c)</t>
+          </r>
         </is>
       </c>
       <c r="AC10" s="47" t="inlineStr">
@@ -5575,17 +5646,70 @@
       </c>
       <c r="AD10" s="46" t="inlineStr">
         <is>
-          <t>s(c/p)</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>s</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>(c/p)</t>
+          </r>
         </is>
       </c>
       <c r="AE10" s="46" t="inlineStr">
         <is>
-          <t>s(d)</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>s</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>(d)</t>
+          </r>
         </is>
       </c>
       <c r="AF10" s="47" t="inlineStr">
         <is>
-          <t>s(psi)</t>
+          <r>
+            <t>s(</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+            </rPr>
+            <t>psi</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>)</t>
+          </r>
         </is>
       </c>
       <c r="AG10" s="23" t="inlineStr">

--- a/docs/verification/files/rocscience/vp049.xlsx
+++ b/docs/verification/files/rocscience/vp049.xlsx
@@ -7639,14 +7639,14 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="56">
+      <c r="A6" s="56" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v/>
+        <v>Layer 1</v>
       </c>
       <c r="B6" s="57" t="n"/>
-      <c r="D6" s="56">
+      <c r="D6" s="56" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v/>
+        <v>Layer 2</v>
       </c>
       <c r="E6" s="57" t="n"/>
       <c r="G6" s="56">
@@ -9282,14 +9282,14 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="58">
+      <c r="A7" s="58" t="str">
         <f>IF(OR(B5="",B5="material"),_xlfn.XLOOKUP(B6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
-        <v/>
+        <v>Layer 1</v>
       </c>
       <c r="B7" s="57" t="n"/>
-      <c r="D7" s="58">
+      <c r="D7" s="58" t="str">
         <f>IF(OR(E5="",E5="material"),_xlfn.XLOOKUP(E6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
-        <v/>
+        <v>Layer 2</v>
       </c>
       <c r="E7" s="57" t="n"/>
       <c r="G7" s="58">
